--- a/src/components/study/excel/topics/004_002_next-gen-array-reshaping-and-grid-transformation/excel_files/array_reshaping_master.xlsx
+++ b/src/components/study/excel/topics/004_002_next-gen-array-reshaping-and-grid-transformation/excel_files/array_reshaping_master.xlsx
@@ -25,44 +25,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="474">
   <si>
     <t>CODER &amp; ACCOTAX</t>
   </si>
   <si>
-    <t>ISO 9001:2015 Certified Centre of Excellence for Coding, Taxation &amp; Advanced Data Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Official Enterprise Practice &amp; Laboratory Master Workbook — EXCEL-PRO-901
-Module: Next-Gen Array Reshaping &amp; Grid Transformation (004_002)
-Campus: 25(10/A) Shibtala Road, Nona Chandan Pukur, Barrackpore, Kolkata 700122</t>
-  </si>
-  <si>
-    <t>🏢  SECTION 1: ORGANISATION PROFILE &amp; CONTACT DETAILS</t>
+    <t>ISO 9001:2015 Certified Centre of Excellence in Computer Science &amp; Financial Modeling</t>
+  </si>
+  <si>
+    <t>Interactive Chapter Practice Workbook · Mentored by Sukanta Hui (28+ Years Exp.) · Barrackpore</t>
+  </si>
+  <si>
+    <t>🏢 1. ORGANISATION PROFILE &amp; CONTACT DETAILS</t>
   </si>
   <si>
     <t>Institute Name</t>
   </si>
   <si>
-    <t>Coder &amp; AccoTax</t>
-  </si>
-  <si>
-    <t>Accreditation</t>
-  </si>
-  <si>
-    <t>ISO 9001:2015 Certified Centre of Excellence for IT &amp; Financial Modeling</t>
-  </si>
-  <si>
-    <t>Registered Campus</t>
+    <t>Coder &amp; AccoTax (Centre of Excellence)</t>
+  </si>
+  <si>
+    <t>Campus Address</t>
   </si>
   <si>
     <t>25(10/A) Shibtala Road, Nona Chandan Pukur, Barrackpore, Kolkata 700122, WB, India</t>
   </si>
   <si>
-    <t>Phone / WhatsApp</t>
-  </si>
-  <si>
-    <t>+91 70037 56860</t>
+    <t>Contact Numbers</t>
+  </si>
+  <si>
+    <t>+91 70037 56860 / +91 84202 04207 (WhatsApp Available)</t>
   </si>
   <si>
     <t>Official Email</t>
@@ -74,16 +66,16 @@
     <t>Web Portal</t>
   </si>
   <si>
-    <t>https://codernaccotax.co.in</t>
-  </si>
-  <si>
-    <t>Core Specializations</t>
-  </si>
-  <si>
-    <t>Full Stack Engineering, Modern Dynamic Arrays, Power Query, DAX, Corporate Taxation</t>
-  </si>
-  <si>
-    <t>👨‍🏫  SECTION 2: LEAD INSTRUCTOR &amp; MASTER MENTOR PROFILE</t>
+    <t>https://www.codernaccotax.co.in</t>
+  </si>
+  <si>
+    <t>Core Domains</t>
+  </si>
+  <si>
+    <t>Full Stack Engineering, Python &amp; Data Science, Advanced Excel, Power BI, Financial Modeling &amp; Taxation</t>
+  </si>
+  <si>
+    <t>👨‍🏫 2. LEAD INSTRUCTOR &amp; MASTER MENTOR PROFILE</t>
   </si>
   <si>
     <t>Lead Instructor</t>
@@ -95,13 +87,13 @@
     <t>Designation</t>
   </si>
   <si>
-    <t>Senior Software Engineer, Corporate Financial Consultant &amp; Lead Academic Mentor</t>
-  </si>
-  <si>
-    <t>Industry Experience</t>
-  </si>
-  <si>
-    <t>27+ Years of Experience in Building Scalable Software Applications &amp; Mentoring (Since May 1998)</t>
+    <t>Senior Software Architect, Corporate Financial Consultant &amp; Lead Academic Mentor</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>28+ Years of Industrial &amp; Academic Mentoring Experience (Since May 1998)</t>
   </si>
   <si>
     <t>GitHub Portfolio</t>
@@ -110,286 +102,184 @@
     <t>https://github.com/sukantahui</t>
   </si>
   <si>
-    <t>Technical Arsenal</t>
-  </si>
-  <si>
-    <t>Python, Advanced Excel 365, Power BI, DAX, SQL, Financial Modeling, React 19, Angular, C, C++</t>
-  </si>
-  <si>
-    <t>Teaching Philosophy</t>
-  </si>
-  <si>
-    <t>Zero-VBA modern spreadsheet architecture using native dynamic vectorization and reshaping.</t>
-  </si>
-  <si>
-    <t>🎓  SECTION 3: COURSE &amp; MODULE ACADEMIC METRICS</t>
-  </si>
-  <si>
-    <t>Curriculum Code &amp; Title</t>
+    <t>Teaching Focus</t>
+  </si>
+  <si>
+    <t>Deep mechanical intuition, edge-case analysis, and production-grade spreadsheet architecture</t>
+  </si>
+  <si>
+    <t>🎓 3. CHAPTER ACADEMIC &amp; MODULE SPECIFICATIONS</t>
+  </si>
+  <si>
+    <t>Course Code &amp; Title</t>
   </si>
   <si>
     <t>EXCEL-PRO-901: Microsoft Excel From Zero to Ultra Expert</t>
   </si>
   <si>
-    <t>Active Module &amp; Slug</t>
-  </si>
-  <si>
-    <t>Next-Gen Array Reshaping &amp; Grid Transformation (004_002_next-gen-array-reshaping-and-grid-transformation)</t>
-  </si>
-  <si>
-    <t>Bloom Taxonomy Level</t>
+    <t>Active Module</t>
+  </si>
+  <si>
+    <t>NEXT GEN ARRAY RESHAPING AND GRID TRANSFORMATION</t>
+  </si>
+  <si>
+    <t>Bloom's Taxonomy</t>
   </si>
   <si>
     <t>Level 4 (Analyze), Level 5 (Evaluate) &amp; Level 6 (Create)</t>
   </si>
   <si>
-    <t>Prerequisites</t>
-  </si>
-  <si>
-    <t>Modern Lookup &amp; Dynamic Array Functions (004_001)</t>
-  </si>
-  <si>
-    <t>Total Module Topics</t>
-  </si>
-  <si>
-    <t>14 Topics (Topic 0 to Topic 13) with 420 Assessment FAQs &amp; Real-World Lab Data</t>
-  </si>
-  <si>
-    <t>📑  SECTION 4: WORKBOOK SHEET DIRECTORY &amp; LAB NAVIGATION</t>
-  </si>
-  <si>
-    <t>Sheet Name</t>
-  </si>
-  <si>
-    <t>Topic ID &amp; Target</t>
-  </si>
-  <si>
-    <t>Primary Functions</t>
-  </si>
-  <si>
-    <t>Dataset Context</t>
-  </si>
-  <si>
-    <t>Rows / Dimension</t>
-  </si>
-  <si>
-    <t>Difficulty</t>
+    <t>📑 4. WORKBOOK SHEET DIRECTORY &amp; QUICK-JUMP NAVIGATION</t>
+  </si>
+  <si>
+    <t>SL #</t>
+  </si>
+  <si>
+    <t>Target Sheet / Topic</t>
+  </si>
+  <si>
+    <t>Primary Formula / Technique</t>
+  </si>
+  <si>
+    <t>Business Context / Dataset</t>
+  </si>
+  <si>
+    <t>🚀 Instant Jump Action</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>Topic0_Overview</t>
   </si>
   <si>
-    <t>Topic 0: Overview</t>
-  </si>
-  <si>
-    <t>All 14 Reshaping Functions</t>
-  </si>
-  <si>
-    <t>Function Classification Matrix</t>
-  </si>
-  <si>
-    <t>11 records</t>
-  </si>
-  <si>
-    <t>Intermediate</t>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Interactive Lab Exercise (004_002_next-gen-array-reshaping-and-grid-transformation)</t>
+  </si>
+  <si>
+    <t>👉 Open Topic0_Overview Sheet</t>
+  </si>
+  <si>
+    <t>Practice Lab</t>
   </si>
   <si>
     <t>Topic1_TOCOL</t>
   </si>
   <si>
-    <t>Topic 1: TOCOL Vector</t>
-  </si>
-  <si>
-    <t>TOCOL(range, ignore, scan)</t>
-  </si>
-  <si>
-    <t>Regional Quarterly Sales Matrix</t>
-  </si>
-  <si>
-    <t>25 records</t>
-  </si>
-  <si>
-    <t>Moderate</t>
+    <t>TOCOL</t>
+  </si>
+  <si>
+    <t>👉 Open Topic1_TOCOL Sheet</t>
   </si>
   <si>
     <t>Topic2_TOROW</t>
   </si>
   <si>
-    <t>Topic 2: TOROW Vector</t>
-  </si>
-  <si>
-    <t>TOROW(range, ignore, scan)</t>
-  </si>
-  <si>
-    <t>Monthly Marketing Spend Matrix</t>
-  </si>
-  <si>
-    <t>10 records</t>
+    <t>TOROW</t>
+  </si>
+  <si>
+    <t>👉 Open Topic2_TOROW Sheet</t>
   </si>
   <si>
     <t>Topic3_CHOOSEROWS</t>
   </si>
   <si>
-    <t>Topic 3: CHOOSEROWS</t>
-  </si>
-  <si>
-    <t>CHOOSEROWS(array, r1, r2)</t>
-  </si>
-  <si>
-    <t>Employee Master Register</t>
-  </si>
-  <si>
-    <t>15 records</t>
-  </si>
-  <si>
-    <t>Advanced</t>
+    <t>CHOOSEROWS</t>
+  </si>
+  <si>
+    <t>👉 Open Topic3_CHOOSEROWS Sheet</t>
   </si>
   <si>
     <t>Topic4_CHOOSECOLS</t>
   </si>
   <si>
-    <t>Topic 4: CHOOSECOLS</t>
-  </si>
-  <si>
-    <t>CHOOSECOLS(array, c1, c2)</t>
-  </si>
-  <si>
-    <t>Corporate Payroll Ledger</t>
+    <t>CHOOSECOLS</t>
+  </si>
+  <si>
+    <t>👉 Open Topic4_CHOOSECOLS Sheet</t>
   </si>
   <si>
     <t>Topic5_TAKE</t>
   </si>
   <si>
-    <t>Topic 5: TAKE Slicing</t>
-  </si>
-  <si>
-    <t>TAKE(array, rows, [cols])</t>
-  </si>
-  <si>
-    <t>Student Performance Rank List</t>
-  </si>
-  <si>
-    <t>12 records</t>
+    <t>TAKE</t>
+  </si>
+  <si>
+    <t>👉 Open Topic5_TAKE Sheet</t>
   </si>
   <si>
     <t>Topic6_DROP</t>
   </si>
   <si>
-    <t>Topic 6: DROP Exclusion</t>
-  </si>
-  <si>
-    <t>DROP(array, rows, [cols])</t>
-  </si>
-  <si>
-    <t>Raw Monthly Financial Report</t>
+    <t>DROP</t>
+  </si>
+  <si>
+    <t>👉 Open Topic6_DROP Sheet</t>
   </si>
   <si>
     <t>Topic7_EXPAND</t>
   </si>
   <si>
-    <t>Topic 7: EXPAND Padding</t>
-  </si>
-  <si>
-    <t>EXPAND(array, rows, cols)</t>
-  </si>
-  <si>
-    <t>Branch Disparate Dimension Data</t>
-  </si>
-  <si>
-    <t>5 records</t>
+    <t>EXPAND</t>
+  </si>
+  <si>
+    <t>👉 Open Topic7_EXPAND Sheet</t>
   </si>
   <si>
     <t>Topic8_WRAPROWS</t>
   </si>
   <si>
-    <t>Topic 8: WRAPROWS</t>
-  </si>
-  <si>
-    <t>WRAPROWS(vector, count)</t>
-  </si>
-  <si>
-    <t>Linear Customer Registration Stream</t>
-  </si>
-  <si>
-    <t>30 items</t>
+    <t>WRAPROWS</t>
+  </si>
+  <si>
+    <t>👉 Open Topic8_WRAPROWS Sheet</t>
   </si>
   <si>
     <t>Topic9_WRAPCOLS</t>
   </si>
   <si>
-    <t>Topic 9: WRAPCOLS</t>
-  </si>
-  <si>
-    <t>WRAPCOLS(vector, count)</t>
-  </si>
-  <si>
-    <t>Academic Timetable Period Stream</t>
-  </si>
-  <si>
-    <t>25 items</t>
+    <t>WRAPCOLS</t>
+  </si>
+  <si>
+    <t>👉 Open Topic9_WRAPCOLS Sheet</t>
   </si>
   <si>
     <t>Topic10_VSTACK_HSTACK</t>
   </si>
   <si>
-    <t>Topic 10: VSTACK &amp; HSTACK</t>
-  </si>
-  <si>
-    <t>VSTACK, HSTACK</t>
-  </si>
-  <si>
-    <t>3 Branch Ledgers &amp; Department KPIs</t>
-  </si>
-  <si>
-    <t>9 records</t>
-  </si>
-  <si>
-    <t>Expert</t>
+    <t>VSTACK HSTACK</t>
+  </si>
+  <si>
+    <t>👉 Open Topic10_VSTACK_HSTACK Sheet</t>
   </si>
   <si>
     <t>Topic11_Matrix_Alignment</t>
   </si>
   <si>
-    <t>Topic 11: Matrix Align</t>
-  </si>
-  <si>
-    <t>TRANSPOSE, VSTACK, TOCOL</t>
-  </si>
-  <si>
-    <t>Multi-Year Budget Schedules</t>
-  </si>
-  <si>
-    <t>6 records</t>
+    <t>Matrix Alignment</t>
+  </si>
+  <si>
+    <t>👉 Open Topic11_Matrix_Alignment Sheet</t>
   </si>
   <si>
     <t>Topic12_Bank_Statement</t>
   </si>
   <si>
-    <t>Topic 12: Bank Statement Project</t>
-  </si>
-  <si>
-    <t>WRAPROWS, CHOOSECOLS, TOCOL</t>
-  </si>
-  <si>
-    <t>Unformatted Multi-Column Bank Dump</t>
-  </si>
-  <si>
-    <t>20 records</t>
+    <t>Bank Statement</t>
+  </si>
+  <si>
+    <t>👉 Open Topic12_Bank_Statement Sheet</t>
   </si>
   <si>
     <t>Topic13_Challenge_Lab</t>
   </si>
   <si>
-    <t>Topic 13: Capstone Challenge</t>
-  </si>
-  <si>
-    <t>VSTACK, CHOOSEROWS, FILTER, TAKE</t>
-  </si>
-  <si>
-    <t>Consolidated Supply Chain Dispatch</t>
-  </si>
-  <si>
-    <t>Mastery</t>
+    <t>Challenge Lab</t>
+  </si>
+  <si>
+    <t>👉 Open Topic13_Challenge_Lab Sheet</t>
   </si>
   <si>
     <t>Function_Name</t>
@@ -410,9 +300,6 @@
     <t>Key_Use_Case</t>
   </si>
   <si>
-    <t>TOCOL</t>
-  </si>
-  <si>
     <t>Vector Flattening</t>
   </si>
   <si>
@@ -428,9 +315,6 @@
     <t>Flatten cross-tab tables into single vertical lists</t>
   </si>
   <si>
-    <t>TOROW</t>
-  </si>
-  <si>
     <t>=TOROW(array, [ignore], [scan_by_col])</t>
   </si>
   <si>
@@ -440,9 +324,6 @@
     <t>Unpivot 2D tables into horizontal banner streams</t>
   </si>
   <si>
-    <t>CHOOSEROWS</t>
-  </si>
-  <si>
     <t>Slicing &amp; Subsetting</t>
   </si>
   <si>
@@ -458,18 +339,12 @@
     <t>Extract specific rows using positive or negative indexes</t>
   </si>
   <si>
-    <t>CHOOSECOLS</t>
-  </si>
-  <si>
     <t>=CHOOSECOLS(array, col_num1, [col_num2]...)</t>
   </si>
   <si>
     <t>Extract and dynamically reorder table columns</t>
   </si>
   <si>
-    <t>TAKE</t>
-  </si>
-  <si>
     <t>Boundary Slicing</t>
   </si>
   <si>
@@ -479,9 +354,6 @@
     <t>Extract Top N or Bottom N records from tables</t>
   </si>
   <si>
-    <t>DROP</t>
-  </si>
-  <si>
     <t>Boundary Exclusion</t>
   </si>
   <si>
@@ -491,9 +363,6 @@
     <t>Strip headers, footers, or margin columns dynamically</t>
   </si>
   <si>
-    <t>EXPAND</t>
-  </si>
-  <si>
     <t>Matrix Resizing</t>
   </si>
   <si>
@@ -509,9 +378,6 @@
     <t>Pad mismatched tables with default values before stacking</t>
   </si>
   <si>
-    <t>WRAPROWS</t>
-  </si>
-  <si>
     <t>Stream Transformation</t>
   </si>
   <si>
@@ -525,9 +391,6 @@
   </si>
   <si>
     <t>Reshape continuous text/number feeds into tabular records</t>
-  </si>
-  <si>
-    <t>WRAPCOLS</t>
   </si>
   <si>
     <t>=WRAPCOLS(vector, wrap_count, [pad_with])</t>
@@ -1593,7 +1456,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="₹#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1604,7 +1467,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="20"/>
+      <sz val="18"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -1615,7 +1478,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="FFFDE68A"/>
+      <color rgb="FFF59E0B"/>
       <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
@@ -1628,7 +1491,7 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -1643,8 +1506,32 @@
       <name val="Segoe UI"/>
     </font>
     <font>
-      <color rgb="FF334155"/>
+      <b/>
+      <color rgb="FF0F172A"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FF0284C7"/>
       <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <color rgb="FF0284C7"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF059669"/>
+      <sz val="8.5"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -1655,11 +1542,11 @@
     </font>
     <font>
       <color rgb="FF1E293B"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1669,6 +1556,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
@@ -1698,7 +1590,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FF334155"/>
       </patternFill>
     </fill>
     <fill>
@@ -1708,7 +1600,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1732,12 +1634,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1759,105 +1676,126 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1882,11 +1820,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>66000</xdr:colOff>
+      <xdr:colOff>14400</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>54000</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1143000" cy="1143000"/>
+    <xdr:ext cx="1047750" cy="1047750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -1902,6 +1840,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>27000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3810000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2243,645 +2220,639 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C1" s="1" t="s">
+    <row r="1" ht="24" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C3" s="2" t="s">
+    <row r="3" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" ht="18" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C4" s="3" t="s">
+    <row r="4" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="5" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="30" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" ht="19" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+    </row>
+    <row r="48" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <v>1</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="D49" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="E49" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="F49" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="10" t="s">
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="18">
+        <v>2</v>
+      </c>
+      <c r="B50" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="C50" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="D50" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="F50" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <v>3</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="C51" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="D51" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="F51" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>4</v>
+      </c>
+      <c r="B52" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="C52" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="D52" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="22" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="F52" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <v>5</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C53" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D53" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="F53" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>6</v>
+      </c>
+      <c r="B54" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="C54" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="D54" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="22" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="F54" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <v>7</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="C55" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="D55" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="F55" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="18">
+        <v>8</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="C56" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="D56" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="F56" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <v>9</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C57" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D57" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="F57" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="18">
+        <v>10</v>
+      </c>
+      <c r="B58" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="C58" s="20" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="D58" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="F58" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <v>11</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C59" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D59" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="F59" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="18">
+        <v>12</v>
+      </c>
+      <c r="B60" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="C60" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="D60" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="F60" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <v>13</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="C61" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="D61" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="F61" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="18">
+        <v>14</v>
+      </c>
+      <c r="B62" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C62" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D62" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>120</v>
+      <c r="F62" s="23" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="AXS0tH3NgUWRwT6WqmTF1rL4x+wG7G9AvuMOzjx4K0h6S5bY05xHEXW4gZHhXAq57YRu71ajlgSh1W1bpBXRVA==" saltValue="/aCpo24bO9nbFufdzxVrSQ==" spinCount="100000"/>
-  <mergeCells count="25">
-    <mergeCell ref="C1:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A31:F31"/>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="vlgQIOq1ggBEW+EJEm1Vmozqjr4xoDuij1QLdgLHXFi2TfbyK45FphJxK48P3vUHwreAvxPc0OIDB0eBE6UtIA==" saltValue="fadRYcbd/wMsyKYnJVExQw==" spinCount="100000" objects="1" scenarios="1"/>
+  <mergeCells count="35">
+    <mergeCell ref="B1:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="A47:F47"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E49" r:id="rId1" tooltip="Click to navigate to Topic0_Overview" location="#'Topic0_Overview'!A1"/>
+    <hyperlink ref="E50" r:id="rId2" tooltip="Click to navigate to Topic1_TOCOL" location="#'Topic1_TOCOL'!A1"/>
+    <hyperlink ref="E51" r:id="rId3" tooltip="Click to navigate to Topic2_TOROW" location="#'Topic2_TOROW'!A1"/>
+    <hyperlink ref="E52" r:id="rId4" tooltip="Click to navigate to Topic3_CHOOSEROWS" location="#'Topic3_CHOOSEROWS'!A1"/>
+    <hyperlink ref="E53" r:id="rId5" tooltip="Click to navigate to Topic4_CHOOSECOLS" location="#'Topic4_CHOOSECOLS'!A1"/>
+    <hyperlink ref="E54" r:id="rId6" tooltip="Click to navigate to Topic5_TAKE" location="#'Topic5_TAKE'!A1"/>
+    <hyperlink ref="E55" r:id="rId7" tooltip="Click to navigate to Topic6_DROP" location="#'Topic6_DROP'!A1"/>
+    <hyperlink ref="E56" r:id="rId8" tooltip="Click to navigate to Topic7_EXPAND" location="#'Topic7_EXPAND'!A1"/>
+    <hyperlink ref="E57" r:id="rId9" tooltip="Click to navigate to Topic8_WRAPROWS" location="#'Topic8_WRAPROWS'!A1"/>
+    <hyperlink ref="E58" r:id="rId10" tooltip="Click to navigate to Topic9_WRAPCOLS" location="#'Topic9_WRAPCOLS'!A1"/>
+    <hyperlink ref="E59" r:id="rId11" tooltip="Click to navigate to Topic10_VSTACK_HSTACK" location="#'Topic10_VSTACK_HSTACK'!A1"/>
+    <hyperlink ref="E60" r:id="rId12" tooltip="Click to navigate to Topic11_Matrix_Alignment" location="#'Topic11_Matrix_Alignment'!A1"/>
+    <hyperlink ref="E61" r:id="rId13" tooltip="Click to navigate to Topic12_Bank_Statement" location="#'Topic12_Bank_Statement'!A1"/>
+    <hyperlink ref="E62" r:id="rId14" tooltip="Click to navigate to Topic13_Challenge_Lab" location="#'Topic13_Challenge_Lab'!A1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -2895,251 +2866,251 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>384</v>
+      <c r="A1" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>385</v>
+      <c r="B2" s="25" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="33">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>234</v>
+      <c r="B3" s="26" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>237</v>
+      <c r="B4" s="25" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>386</v>
+      <c r="B5" s="26" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>387</v>
+      <c r="B6" s="25" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>388</v>
+      <c r="B7" s="26" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="32">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>239</v>
+      <c r="B8" s="25" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="33">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>242</v>
+      <c r="B9" s="26" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="A10" s="32">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>389</v>
+      <c r="B10" s="25" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="33">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>390</v>
+      <c r="B11" s="26" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="A12" s="32">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>391</v>
+      <c r="B12" s="25" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>244</v>
+      <c r="B13" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="A14" s="32">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>247</v>
+      <c r="B14" s="25" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="33">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>392</v>
+      <c r="B15" s="26" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="25">
+      <c r="A16" s="32">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>393</v>
+      <c r="B16" s="25" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="33">
         <v>16</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>394</v>
+      <c r="B17" s="26" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+      <c r="A18" s="32">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>249</v>
+      <c r="B18" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="33">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>252</v>
+      <c r="B19" s="26" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="25">
+      <c r="A20" s="32">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>395</v>
+      <c r="B20" s="25" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="33">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>396</v>
+      <c r="B21" s="26" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="25">
+      <c r="A22" s="32">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>397</v>
+      <c r="B22" s="25" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="A23" s="33">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>254</v>
+      <c r="B23" s="26" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="25">
+      <c r="A24" s="32">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>256</v>
+      <c r="B24" s="25" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+      <c r="A25" s="33">
         <v>24</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>398</v>
+      <c r="B25" s="26" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="25">
+      <c r="A26" s="32">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>399</v>
+      <c r="B26" s="25" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="26">
+      <c r="A27" s="33">
         <v>26</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>400</v>
+      <c r="B27" s="26" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+      <c r="A28" s="32">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>258</v>
+      <c r="B28" s="25" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
+      <c r="A29" s="33">
         <v>28</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>261</v>
+      <c r="B29" s="26" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="25">
+      <c r="A30" s="32">
         <v>29</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>259</v>
+      <c r="B30" s="25" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="26">
+      <c r="A31" s="33">
         <v>30</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>401</v>
+      <c r="B31" s="26" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3158,211 +3129,211 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>402</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>403</v>
+      <c r="A1" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>404</v>
+      <c r="B2" s="25" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="33">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>405</v>
+      <c r="B3" s="26" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>406</v>
+      <c r="B4" s="25" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>407</v>
+      <c r="B5" s="26" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>408</v>
+      <c r="B6" s="25" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>409</v>
+      <c r="B7" s="26" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="32">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>410</v>
+      <c r="B8" s="25" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="33">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>411</v>
+      <c r="B9" s="26" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="A10" s="32">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>412</v>
+      <c r="B10" s="25" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="33">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>413</v>
+      <c r="B11" s="26" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="A12" s="32">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>414</v>
+      <c r="B12" s="25" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>415</v>
+      <c r="B13" s="26" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="A14" s="32">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>416</v>
+      <c r="B14" s="25" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="33">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>417</v>
+      <c r="B15" s="26" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="25">
+      <c r="A16" s="32">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>418</v>
+      <c r="B16" s="25" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="33">
         <v>16</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>419</v>
+      <c r="B17" s="26" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+      <c r="A18" s="32">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>420</v>
+      <c r="B18" s="25" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="33">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>421</v>
+      <c r="B19" s="26" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="25">
+      <c r="A20" s="32">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>422</v>
+      <c r="B20" s="25" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="33">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>423</v>
+      <c r="B21" s="26" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="25">
+      <c r="A22" s="32">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>424</v>
+      <c r="B22" s="25" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="A23" s="33">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>425</v>
+      <c r="B23" s="26" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="25">
+      <c r="A24" s="32">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>426</v>
+      <c r="B24" s="25" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+      <c r="A25" s="33">
         <v>24</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>427</v>
+      <c r="B25" s="26" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="25">
+      <c r="A26" s="32">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>428</v>
+      <c r="B26" s="25" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -3384,203 +3355,203 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>430</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>433</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>434</v>
+      <c r="A1" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>435</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="E2" s="21">
+      <c r="A2" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="E2" s="28">
         <v>9500</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>437</v>
+      <c r="F2" s="25" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="E3" s="22">
+      <c r="A3" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E3" s="29">
         <v>16000</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>440</v>
+      <c r="F3" s="26" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>441</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="E4" s="21">
+      <c r="A4" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="E4" s="28">
         <v>12500</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>437</v>
+      <c r="F4" s="25" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="E5" s="22">
+      <c r="A5" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="29">
         <v>11000</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>445</v>
+      <c r="F5" s="26" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="E6" s="21">
+      <c r="A6" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" s="28">
         <v>8500</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>437</v>
+      <c r="F6" s="25" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="A7" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="29">
         <v>9000</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>437</v>
+      <c r="F7" s="26" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>448</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>451</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>452</v>
-      </c>
-      <c r="E8" s="21">
+      <c r="A8" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="28">
         <v>7800</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>440</v>
+      <c r="F8" s="25" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="E9" s="22">
+      <c r="A9" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>409</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="29">
         <v>13500</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>437</v>
+      <c r="F9" s="26" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>457</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="A10" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="E10" s="28">
         <v>10500</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>445</v>
+      <c r="F10" s="25" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -3600,122 +3571,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>461</v>
+      <c r="A1" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="B2" s="21">
+      <c r="A2" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="B2" s="28">
         <v>1200000</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="28">
         <v>1500000</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="28">
         <v>1850000</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>463</v>
+      <c r="E2" s="25" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" s="29">
         <v>950000</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="29">
         <v>1300000</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="29">
         <v>1700000</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>465</v>
+      <c r="E3" s="26" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="B4" s="21">
+      <c r="A4" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" s="28">
         <v>800000</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="28">
         <v>920000</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="28">
         <v>1100000</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>467</v>
+      <c r="E4" s="25" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="B5" s="22">
+      <c r="A5" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="B5" s="29">
         <v>1100000</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="29">
         <v>1280000</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="29">
         <v>1450000</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>469</v>
+      <c r="E5" s="26" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="B6" s="21">
+      <c r="A6" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" s="28">
         <v>650000</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="28">
         <v>850000</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="28">
         <v>1150000</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>471</v>
+      <c r="E6" s="25" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="A7" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="B7" s="29">
         <v>500000</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="29">
         <v>600000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>720000</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>473</v>
+      <c r="E7" s="26" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3735,233 +3706,233 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>474</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>475</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>476</v>
+      <c r="A1" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>478</v>
+      <c r="B2" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="33">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>480</v>
+      <c r="B3" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>482</v>
+      <c r="B4" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>484</v>
+      <c r="B5" s="26" t="s">
+        <v>438</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="B6" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" s="38">
         <v>9500</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>486</v>
+      <c r="B7" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="32">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>487</v>
+      <c r="B8" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="33">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>488</v>
+      <c r="B9" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="A10" s="32">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>484</v>
+      <c r="B10" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="33">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="C11" s="30">
+      <c r="B11" s="26" t="s">
+        <v>440</v>
+      </c>
+      <c r="C11" s="37">
         <v>12000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="A12" s="32">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>489</v>
+      <c r="B12" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>490</v>
+      <c r="B13" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="A14" s="32">
         <v>13</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>491</v>
+      <c r="B14" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+      <c r="A15" s="33">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>484</v>
+      <c r="B15" s="26" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="25">
+      <c r="A16" s="32">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="C16" s="31">
+      <c r="B16" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="C16" s="38">
         <v>8500</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+      <c r="A17" s="33">
         <v>16</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>492</v>
+      <c r="B17" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="25">
+      <c r="A18" s="32">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>493</v>
+      <c r="B18" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="A19" s="33">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>494</v>
+      <c r="B19" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="25">
+      <c r="A20" s="32">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>495</v>
+      <c r="B20" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="A21" s="33">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="C21" s="30">
+      <c r="B21" s="26" t="s">
+        <v>440</v>
+      </c>
+      <c r="C21" s="37">
         <v>35000</v>
       </c>
     </row>
@@ -3984,256 +3955,256 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>501</v>
+      <c r="A1" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D2" s="25">
+      <c r="A2" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="32">
         <v>12.5</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F2" s="21">
+      <c r="E2" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="F2" s="28">
         <v>1250</v>
       </c>
-      <c r="G2" s="18" t="s">
-        <v>504</v>
+      <c r="G2" s="25" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>505</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="26">
+      <c r="A3" s="26" t="s">
+        <v>460</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="33">
         <v>8.2</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>506</v>
-      </c>
-      <c r="F3" s="22">
+      <c r="E3" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="F3" s="29">
         <v>650</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>507</v>
+      <c r="G3" s="26" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="D4" s="25">
+      <c r="A4" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="32">
         <v>15</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F4" s="21">
+      <c r="E4" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="F4" s="28">
         <v>1500</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>509</v>
+      <c r="G4" s="25" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>510</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D5" s="26">
+      <c r="A5" s="26" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="33">
         <v>22.4</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>511</v>
-      </c>
-      <c r="F5" s="22">
+      <c r="E5" s="26" t="s">
+        <v>466</v>
+      </c>
+      <c r="F5" s="29">
         <v>2200</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>507</v>
+      <c r="G5" s="26" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="A6" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="32">
         <v>6.8</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="F6" s="21">
+      <c r="E6" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="F6" s="28">
         <v>550</v>
       </c>
-      <c r="G6" s="18" t="s">
-        <v>504</v>
+      <c r="G6" s="25" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>513</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>514</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="A7" s="26" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>469</v>
+      </c>
+      <c r="D7" s="33">
         <v>3.5</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E7" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="29">
         <v>450</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>507</v>
+      <c r="G7" s="26" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="A8" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="32">
         <v>11</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="F8" s="21">
+      <c r="E8" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="F8" s="28">
         <v>880</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>507</v>
+      <c r="G8" s="25" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="D9" s="26">
+      <c r="A9" s="26" t="s">
+        <v>471</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="33">
         <v>9.4</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>506</v>
-      </c>
-      <c r="F9" s="22">
+      <c r="E9" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="F9" s="29">
         <v>750</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>509</v>
+      <c r="G9" s="26" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="A10" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="32">
         <v>18.2</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="F10" s="21">
+      <c r="E10" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="F10" s="28">
         <v>1800</v>
       </c>
-      <c r="G10" s="18" t="s">
-        <v>507</v>
+      <c r="G10" s="25" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>518</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="A11" s="26" t="s">
+        <v>473</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="33">
         <v>5.2</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="F11" s="22">
+      <c r="E11" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="F11" s="29">
         <v>600</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>504</v>
+      <c r="G11" s="26" t="s">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -4256,243 +4227,243 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="17" t="s">
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D10" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="F10" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="17" t="s">
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="B11" s="26" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="C11" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="D11" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="E11" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="F11" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="18" t="s">
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="B12" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="D12" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="F12" s="25" t="s">
         <v>134</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4511,444 +4482,444 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>184</v>
+      <c r="A1" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="21">
+      <c r="A2" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="28">
         <v>145000</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="28">
         <v>168000</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="28">
         <v>192000</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="28">
         <v>215000</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="29">
         <v>98000</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="22">
+      <c r="C3" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="29">
         <v>115000</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="29">
         <v>132000</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="21">
+      <c r="A4" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="28">
         <v>112000</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="28">
         <v>124000</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="21">
+      <c r="D4" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="28">
         <v>148000</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="22">
+      <c r="A5" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="29">
         <v>178000</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="29">
         <v>195000</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="29">
         <v>210000</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="29">
         <v>245000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="21">
+      <c r="A6" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="28">
         <v>85000</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="28">
         <v>92000</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="28">
         <v>99000</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>187</v>
+      <c r="E6" s="25" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="A7" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="29">
         <v>320000</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="29">
         <v>345000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>380000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="29">
         <v>410000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="21">
+      <c r="A8" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="28">
         <v>135000</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="28">
         <v>148000</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="28">
         <v>162000</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="28">
         <v>175000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="29">
         <v>92000</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="29">
         <v>104000</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="29">
         <v>118000</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="29">
         <v>129000</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="A10" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="28">
         <v>210000</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="28">
         <v>228000</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="28">
         <v>252000</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="28">
         <v>280000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="29">
         <v>125000</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="29">
         <v>138000</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="29">
         <v>154000</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="29">
         <v>168000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="21">
+      <c r="A12" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="28">
         <v>275000</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="28">
         <v>295000</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="28">
         <v>318000</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="28">
         <v>350000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="22">
+      <c r="A13" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="29">
         <v>140000</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="29">
         <v>155000</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="29">
         <v>170000</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="29">
         <v>188000</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B14" s="21">
+      <c r="A14" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="28">
         <v>88000</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="28">
         <v>96000</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="28">
         <v>108000</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="28">
         <v>119000</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B15" s="22">
+      <c r="A15" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="29">
         <v>115000</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="29">
         <v>128000</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="29">
         <v>142000</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="29">
         <v>158000</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B16" s="21">
+      <c r="A16" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="28">
         <v>340000</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="28">
         <v>375000</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="28">
         <v>410000</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="28">
         <v>460000</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="22">
+      <c r="A17" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="29">
         <v>420000</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="29">
         <v>465000</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="29">
         <v>510000</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="29">
         <v>580000</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B18" s="21">
+      <c r="A18" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="28">
         <v>260000</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="28">
         <v>285000</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="28">
         <v>310000</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="28">
         <v>340000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B19" s="22">
+      <c r="A19" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="29">
         <v>105000</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="29">
         <v>118000</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="29">
         <v>130000</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="29">
         <v>145000</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B20" s="21">
+      <c r="A20" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="28">
         <v>130000</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="28">
         <v>142000</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="28">
         <v>158000</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="28">
         <v>172000</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21" s="22">
+      <c r="A21" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="29">
         <v>165000</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="29">
         <v>182000</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="29">
         <v>198000</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="29">
         <v>220000</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="28">
         <v>150000</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="28">
         <v>168000</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="28">
         <v>185000</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="28">
         <v>205000</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B23" s="22">
+      <c r="A23" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="29">
         <v>142000</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="29">
         <v>156000</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="29">
         <v>172000</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="29">
         <v>190000</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="28">
         <v>120000</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="28">
         <v>134000</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="28">
         <v>148000</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="28">
         <v>164000</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25" s="22">
+      <c r="A25" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="29">
         <v>138000</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="29">
         <v>152000</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="29">
         <v>166000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="29">
         <v>182000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="28">
         <v>185000</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="28">
         <v>205000</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="28">
         <v>228000</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="28">
         <v>255000</v>
       </c>
     </row>
@@ -4968,222 +4939,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>216</v>
+      <c r="A1" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B2" s="21">
+      <c r="A2" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="28">
         <v>45000</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="28">
         <v>52000</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="28">
         <v>58000</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="28">
         <v>64000</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="28">
         <v>70000</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="29">
         <v>38000</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="29">
         <v>42000</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="29">
         <v>49000</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="29">
         <v>55000</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="29">
         <v>62000</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B4" s="21">
+      <c r="A4" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="28">
         <v>25000</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="28">
         <v>28000</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="28">
         <v>34000</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="28">
         <v>39000</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="28">
         <v>45000</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" s="22">
+      <c r="A5" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="29">
         <v>30000</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="29">
         <v>35000</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="29">
         <v>40000</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="29">
         <v>44000</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="29">
         <v>48000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="21">
+      <c r="A6" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="28">
         <v>50000</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="28">
         <v>50000</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="28">
         <v>50000</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="28">
         <v>50000</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="28">
         <v>50000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="22">
+      <c r="A7" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="29">
         <v>15000</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="29">
         <v>18000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="29">
         <v>16000</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="29">
         <v>19000</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="29">
         <v>22000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="21">
+      <c r="A8" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="28">
         <v>8000</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="28">
         <v>9500</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="28">
         <v>11000</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="28">
         <v>12500</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="28">
         <v>14000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="29">
         <v>6000</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="29">
         <v>6500</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="29">
         <v>7200</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="29">
         <v>8000</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="29">
         <v>9000</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="A10" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="28">
         <v>20000</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="28">
         <v>25000</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="28">
         <v>30000</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="28">
         <v>35000</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="28">
         <v>40000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="29">
         <v>5000</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="29">
         <v>5500</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="29">
         <v>6000</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="29">
         <v>6500</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="29">
         <v>7000</v>
       </c>
     </row>
@@ -5208,370 +5179,370 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="32">
+        <v>6</v>
+      </c>
+      <c r="G2" s="28">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="33">
+        <v>5</v>
+      </c>
+      <c r="G3" s="29">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="32">
+        <v>7</v>
+      </c>
+      <c r="G4" s="28">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="33">
+        <v>8</v>
+      </c>
+      <c r="G5" s="29">
+        <v>98000</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="32">
+        <v>9</v>
+      </c>
+      <c r="G6" s="28">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="33">
+        <v>4</v>
+      </c>
+      <c r="G7" s="29">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="32">
+        <v>5</v>
+      </c>
+      <c r="G8" s="28">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="33">
+        <v>3</v>
+      </c>
+      <c r="G9" s="29">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C10" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="E10" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="F10" s="32">
+        <v>6</v>
+      </c>
+      <c r="G10" s="28">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="B11" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="C11" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="E11" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="F11" s="33">
+        <v>4</v>
+      </c>
+      <c r="G11" s="29">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="B12" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="C12" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E12" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="32">
+        <v>5</v>
+      </c>
+      <c r="G12" s="28">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="F2" s="25">
+      <c r="B13" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="F13" s="33">
+        <v>3</v>
+      </c>
+      <c r="G13" s="29">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="32">
+        <v>10</v>
+      </c>
+      <c r="G14" s="28">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="F15" s="33">
         <v>6</v>
       </c>
-      <c r="G2" s="21">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="F3" s="26">
-        <v>5</v>
-      </c>
-      <c r="G3" s="22">
-        <v>78000</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" s="25">
-        <v>7</v>
-      </c>
-      <c r="G4" s="21">
-        <v>92000</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="G15" s="29">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="B16" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="C16" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E16" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="F5" s="26">
-        <v>8</v>
-      </c>
-      <c r="G5" s="22">
-        <v>98000</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="F6" s="25">
-        <v>9</v>
-      </c>
-      <c r="G6" s="21">
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F7" s="26">
+      <c r="F16" s="32">
         <v>4</v>
       </c>
-      <c r="G7" s="22">
-        <v>62000</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="25">
-        <v>5</v>
-      </c>
-      <c r="G8" s="21">
-        <v>68000</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F9" s="26">
-        <v>3</v>
-      </c>
-      <c r="G9" s="22">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10" s="25">
-        <v>6</v>
-      </c>
-      <c r="G10" s="21">
-        <v>82000</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F11" s="26">
-        <v>4</v>
-      </c>
-      <c r="G11" s="22">
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" s="25">
-        <v>5</v>
-      </c>
-      <c r="G12" s="21">
-        <v>79000</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="F13" s="26">
-        <v>3</v>
-      </c>
-      <c r="G13" s="22">
-        <v>58000</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="F14" s="25">
-        <v>10</v>
-      </c>
-      <c r="G14" s="21">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="F15" s="26">
-        <v>6</v>
-      </c>
-      <c r="G15" s="22">
-        <v>76000</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="F16" s="25">
-        <v>4</v>
-      </c>
-      <c r="G16" s="21">
+      <c r="G16" s="28">
         <v>65000</v>
       </c>
     </row>
@@ -5594,354 +5565,354 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>306</v>
+      <c r="A1" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="28">
+        <v>50000</v>
+      </c>
+      <c r="G2" s="28">
+        <v>25000</v>
+      </c>
+      <c r="H2" s="28">
+        <v>6000</v>
+      </c>
+      <c r="I2" s="28">
+        <v>75000</v>
+      </c>
+      <c r="J2" s="28">
+        <v>69000</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="29">
+        <v>46000</v>
+      </c>
+      <c r="G3" s="29">
+        <v>23000</v>
+      </c>
+      <c r="H3" s="29">
+        <v>5520</v>
+      </c>
+      <c r="I3" s="29">
+        <v>69000</v>
+      </c>
+      <c r="J3" s="29">
+        <v>63480</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="28">
+        <v>54000</v>
+      </c>
+      <c r="G4" s="28">
+        <v>27000</v>
+      </c>
+      <c r="H4" s="28">
+        <v>6480</v>
+      </c>
+      <c r="I4" s="28">
+        <v>81000</v>
+      </c>
+      <c r="J4" s="28">
+        <v>74520</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="29">
+        <v>58000</v>
+      </c>
+      <c r="G5" s="29">
+        <v>29000</v>
+      </c>
+      <c r="H5" s="29">
+        <v>6960</v>
+      </c>
+      <c r="I5" s="29">
+        <v>87000</v>
+      </c>
+      <c r="J5" s="29">
+        <v>80040</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="28">
+        <v>68000</v>
+      </c>
+      <c r="G6" s="28">
+        <v>34000</v>
+      </c>
+      <c r="H6" s="28">
+        <v>8160</v>
+      </c>
+      <c r="I6" s="28">
+        <v>102000</v>
+      </c>
+      <c r="J6" s="28">
+        <v>93840</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="29">
+        <v>36000</v>
+      </c>
+      <c r="G7" s="29">
+        <v>18000</v>
+      </c>
+      <c r="H7" s="29">
+        <v>4320</v>
+      </c>
+      <c r="I7" s="29">
+        <v>54000</v>
+      </c>
+      <c r="J7" s="29">
+        <v>49680</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="28">
+        <v>40000</v>
+      </c>
+      <c r="G8" s="28">
+        <v>20000</v>
+      </c>
+      <c r="H8" s="28">
+        <v>4800</v>
+      </c>
+      <c r="I8" s="28">
+        <v>60000</v>
+      </c>
+      <c r="J8" s="28">
+        <v>55200</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="29">
+        <v>32000</v>
+      </c>
+      <c r="G9" s="29">
+        <v>16000</v>
+      </c>
+      <c r="H9" s="29">
+        <v>3840</v>
+      </c>
+      <c r="I9" s="29">
+        <v>48000</v>
+      </c>
+      <c r="J9" s="29">
+        <v>44160</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="28">
+        <v>48000</v>
+      </c>
+      <c r="G10" s="28">
+        <v>24000</v>
+      </c>
+      <c r="H10" s="28">
+        <v>5760</v>
+      </c>
+      <c r="I10" s="28">
+        <v>72000</v>
+      </c>
+      <c r="J10" s="28">
+        <v>66240</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="21">
-        <v>50000</v>
-      </c>
-      <c r="G2" s="21">
-        <v>25000</v>
-      </c>
-      <c r="H2" s="21">
-        <v>6000</v>
-      </c>
-      <c r="I2" s="21">
-        <v>75000</v>
-      </c>
-      <c r="J2" s="21">
-        <v>69000</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="F3" s="22">
-        <v>46000</v>
-      </c>
-      <c r="G3" s="22">
-        <v>23000</v>
-      </c>
-      <c r="H3" s="22">
-        <v>5520</v>
-      </c>
-      <c r="I3" s="22">
-        <v>69000</v>
-      </c>
-      <c r="J3" s="22">
-        <v>63480</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4" s="21">
-        <v>54000</v>
-      </c>
-      <c r="G4" s="21">
-        <v>27000</v>
-      </c>
-      <c r="H4" s="21">
-        <v>6480</v>
-      </c>
-      <c r="I4" s="21">
-        <v>81000</v>
-      </c>
-      <c r="J4" s="21">
-        <v>74520</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F5" s="22">
-        <v>58000</v>
-      </c>
-      <c r="G5" s="22">
-        <v>29000</v>
-      </c>
-      <c r="H5" s="22">
-        <v>6960</v>
-      </c>
-      <c r="I5" s="22">
-        <v>87000</v>
-      </c>
-      <c r="J5" s="22">
-        <v>80040</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="F6" s="21">
-        <v>68000</v>
-      </c>
-      <c r="G6" s="21">
-        <v>34000</v>
-      </c>
-      <c r="H6" s="21">
-        <v>8160</v>
-      </c>
-      <c r="I6" s="21">
-        <v>102000</v>
-      </c>
-      <c r="J6" s="21">
-        <v>93840</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="F7" s="22">
-        <v>36000</v>
-      </c>
-      <c r="G7" s="22">
-        <v>18000</v>
-      </c>
-      <c r="H7" s="22">
-        <v>4320</v>
-      </c>
-      <c r="I7" s="22">
-        <v>54000</v>
-      </c>
-      <c r="J7" s="22">
-        <v>49680</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="21">
-        <v>40000</v>
-      </c>
-      <c r="G8" s="21">
-        <v>20000</v>
-      </c>
-      <c r="H8" s="21">
-        <v>4800</v>
-      </c>
-      <c r="I8" s="21">
-        <v>60000</v>
-      </c>
-      <c r="J8" s="21">
-        <v>55200</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F9" s="22">
-        <v>32000</v>
-      </c>
-      <c r="G9" s="22">
-        <v>16000</v>
-      </c>
-      <c r="H9" s="22">
-        <v>3840</v>
-      </c>
-      <c r="I9" s="22">
-        <v>48000</v>
-      </c>
-      <c r="J9" s="22">
-        <v>44160</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10" s="21">
-        <v>48000</v>
-      </c>
-      <c r="G10" s="21">
-        <v>24000</v>
-      </c>
-      <c r="H10" s="21">
-        <v>5760</v>
-      </c>
-      <c r="I10" s="21">
-        <v>72000</v>
-      </c>
-      <c r="J10" s="21">
-        <v>66240</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F11" s="22">
+      <c r="F11" s="29">
         <v>38000</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="29">
         <v>19000</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="29">
         <v>4560</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="29">
         <v>57000</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="29">
         <v>52440</v>
       </c>
     </row>
@@ -5965,341 +5936,341 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>340</v>
+      <c r="A1" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="25">
+      <c r="B2" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="32">
         <v>99</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="32">
         <v>96</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="32">
         <v>98</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="32">
         <v>293</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>341</v>
+      <c r="H2" s="25" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+      <c r="A3" s="33">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="26">
+      <c r="B3" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="33">
         <v>98</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="33">
         <v>97</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="33">
         <v>95</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="33">
         <v>290</v>
       </c>
-      <c r="H3" s="19" t="s">
-        <v>341</v>
+      <c r="H3" s="26" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D4" s="25">
+      <c r="B4" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="32">
         <v>97</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="32">
         <v>95</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="32">
         <v>96</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="32">
         <v>288</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>341</v>
+      <c r="H4" s="25" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5" s="26">
+      <c r="B5" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="33">
         <v>96</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="33">
         <v>94</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="33">
         <v>97</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="33">
         <v>287</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>342</v>
+      <c r="H5" s="26" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="B6" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" s="32">
         <v>95</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="32">
         <v>93</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="32">
         <v>94</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="32">
         <v>282</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>342</v>
+      <c r="H6" s="25" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="33">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="B7" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="33">
         <v>92</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="33">
         <v>91</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="33">
         <v>93</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="33">
         <v>276</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>342</v>
+      <c r="H7" s="26" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="32">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="B8" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="32">
         <v>90</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="32">
         <v>89</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="32">
         <v>91</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="32">
         <v>270</v>
       </c>
-      <c r="H8" s="18" t="s">
-        <v>343</v>
+      <c r="H8" s="25" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+      <c r="A9" s="33">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="D9" s="26">
+      <c r="B9" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="33">
         <v>88</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="33">
         <v>87</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="33">
         <v>90</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="33">
         <v>265</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>343</v>
+      <c r="H9" s="26" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
+      <c r="A10" s="32">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="B10" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="32">
         <v>86</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="32">
         <v>85</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="32">
         <v>88</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="32">
         <v>259</v>
       </c>
-      <c r="H10" s="18" t="s">
-        <v>343</v>
+      <c r="H10" s="25" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+      <c r="A11" s="33">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="B11" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="33">
         <v>84</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="33">
         <v>82</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="33">
         <v>85</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="33">
         <v>251</v>
       </c>
-      <c r="H11" s="19" t="s">
-        <v>344</v>
+      <c r="H11" s="26" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="A12" s="32">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="D12" s="25">
+      <c r="B12" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="32">
         <v>82</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="32">
         <v>80</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="32">
         <v>83</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="32">
         <v>245</v>
       </c>
-      <c r="H12" s="18" t="s">
-        <v>344</v>
+      <c r="H12" s="25" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+      <c r="A13" s="33">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" s="26">
+      <c r="B13" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="33">
         <v>79</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="33">
         <v>78</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="33">
         <v>81</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="33">
         <v>238</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>345</v>
+      <c r="H13" s="26" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -6320,224 +6291,224 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>347</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>350</v>
+      <c r="A1" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>187</v>
+      <c r="A2" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>187</v>
+      <c r="A3" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>357</v>
+      <c r="A4" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="D5" s="30">
+      <c r="A5" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="37">
         <v>45000</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="37">
         <v>8100</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6" s="31">
+      <c r="A6" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="38">
         <v>38000</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="38">
         <v>6840</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7" s="30">
+      <c r="A7" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="37">
         <v>52000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="37">
         <v>9360</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D8" s="31">
+      <c r="A8" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D8" s="38">
         <v>61000</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="38">
         <v>10980</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="30">
+      <c r="A9" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="37">
         <v>74000</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="37">
         <v>13320</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="A10" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="38">
         <v>29000</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="38">
         <v>5220</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="D11" s="30">
+      <c r="A11" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" s="37">
         <v>35000</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="37">
         <v>6300</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="D12" s="31">
+      <c r="A12" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="38">
         <v>334000</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="38">
         <v>60120</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>187</v>
+      <c r="A13" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -6558,86 +6529,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>370</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>372</v>
+      <c r="A1" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="C2" s="25">
+      <c r="A2" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" s="32">
         <v>150</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="28">
         <v>650</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C3" s="26">
+      <c r="A3" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="33">
         <v>120</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="29">
         <v>950</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="A4" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="C4" s="32">
         <v>95</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="28">
         <v>800</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C5" s="26">
+      <c r="A5" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="C5" s="33">
         <v>180</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="29">
         <v>550</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="A6" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="32">
         <v>80</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="28">
         <v>1100</v>
       </c>
     </row>
